--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-05-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שחר לוטטי - An Den Isoun Esi Cover</v>
+        <v>יעקב מלכי - שעות לא שעות קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-03</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410665&amp;sid=455ab9b1ff41ca83611ba32f60585b94</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410683&amp;sid=27bae473bfbefcf3b372051115b6e45a</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שחר לוטטי - An Den Isoun Esi Cover</v>
+        <v>יעקב מלכי - שעות לא שעות קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>עמרי ישראל - ניגע אל החלום קאבר</v>
+        <v>גל וקנין - שלווה בארמונתייך קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-03</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410663&amp;sid=455ab9b1ff41ca83611ba32f60585b94</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410680&amp;sid=27bae473bfbefcf3b372051115b6e45a</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,88 +507,12 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>עמרי ישראל - ניגע אל החלום קאבר</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>אוראל מנצור - האיש ההוא קאבר</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410658&amp;sid=455ab9b1ff41ca83611ba32f60585b94</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>אוראל מנצור - האיש ההוא קאבר</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>אבישי עוזיאל - Still Not Goodbye Cover</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410657&amp;sid=455ab9b1ff41ca83611ba32f60585b94</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>אבישי עוזיאל - Still Not Goodbye Cover</v>
+        <v>גל וקנין - שלווה בארמונתייך קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>